--- a/幼儿受伤处理记录/幼儿受伤记录表.xlsx
+++ b/幼儿受伤处理记录/幼儿受伤记录表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\XuChe\幼儿受伤处理记录\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\XuChe\幼儿受伤处理记录\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="10880" activeTab="1"/>
+    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="162">
   <si>
     <t>幼儿受伤记录表 · 使用说明（详细版见同目录《使用说明.txt》）</t>
   </si>
@@ -190,9 +190,6 @@
     <t>杨老师(班主任)</t>
   </si>
   <si>
-    <t>04-001</t>
-  </si>
-  <si>
     <t xml:space="preserve">根据园方描述和监控，事发时班级里只有一个老师，正常是配备4个老师。
 </t>
   </si>
@@ -204,9 +201,6 @@
   </si>
   <si>
     <t>滨江儿保急诊清创缝合7针，整形科门诊</t>
-  </si>
-  <si>
-    <t>02-001</t>
   </si>
   <si>
     <t>A003</t>
@@ -289,7 +283,25 @@
     <t>A011</t>
   </si>
   <si>
+    <t>杭整换药</t>
+  </si>
+  <si>
     <t>A012</t>
+  </si>
+  <si>
+    <t>A013</t>
+  </si>
+  <si>
+    <t>A014</t>
+  </si>
+  <si>
+    <t>A015</t>
+  </si>
+  <si>
+    <t>A016</t>
+  </si>
+  <si>
+    <t>A017</t>
   </si>
   <si>
     <t>日期</t>
@@ -570,10 +582,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -1091,19 +1103,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1623,12 +1635,12 @@
     <tabColor rgb="FF808080"/>
   </sheetPr>
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" spans="1:1">
+    <row r="1" ht="20.4" spans="1:1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1638,27 +1650,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:1">
+    <row r="3" ht="16.2" spans="1:1">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="14.5" spans="1:1">
+    <row r="4" ht="15" spans="1:1">
       <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="14.5" spans="1:1">
+    <row r="5" ht="15" spans="1:1">
       <c r="A5" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="14.5" spans="1:1">
+    <row r="6" ht="15" spans="1:1">
       <c r="A6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="14.5" spans="1:1">
+    <row r="7" ht="15" spans="1:1">
       <c r="A7" s="11" t="s">
         <v>6</v>
       </c>
@@ -1668,17 +1680,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:1">
+    <row r="9" ht="16.2" spans="1:1">
       <c r="A9" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" ht="14.5" spans="1:1">
+    <row r="10" ht="15" spans="1:1">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="14.5" spans="1:1">
+    <row r="11" ht="15" spans="1:1">
       <c r="A11" s="11" t="s">
         <v>9</v>
       </c>
@@ -1688,27 +1700,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:1">
+    <row r="13" ht="16.2" spans="1:1">
       <c r="A13" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="14.5" spans="1:1">
+    <row r="14" ht="15" spans="1:1">
       <c r="A14" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" ht="14.5" spans="1:1">
+    <row r="15" ht="15" spans="1:1">
       <c r="A15" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" ht="14.5" spans="1:1">
+    <row r="16" ht="15" spans="1:1">
       <c r="A16" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" ht="14.5" spans="1:1">
+    <row r="17" ht="15" spans="1:1">
       <c r="A17" s="11" t="s">
         <v>14</v>
       </c>
@@ -1718,17 +1730,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="16.5" spans="1:1">
+    <row r="19" ht="16.2" spans="1:1">
       <c r="A19" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" ht="14.5" spans="1:1">
+    <row r="20" ht="15.6" spans="1:1">
       <c r="A20" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" ht="14.5" spans="1:1">
+    <row r="21" ht="15" spans="1:1">
       <c r="A21" s="11" t="s">
         <v>17</v>
       </c>
@@ -1738,22 +1750,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="16.5" spans="1:1">
+    <row r="23" ht="16.2" spans="1:1">
       <c r="A23" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" ht="14.5" spans="1:1">
+    <row r="24" ht="15" spans="1:1">
       <c r="A24" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" ht="14.5" spans="1:1">
+    <row r="25" ht="15" spans="1:1">
       <c r="A25" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" ht="14.5" spans="1:1">
+    <row r="26" ht="15" spans="1:1">
       <c r="A26" s="11" t="s">
         <v>21</v>
       </c>
@@ -1763,7 +1775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="14.5" spans="1:1">
+    <row r="28" ht="15" spans="1:1">
       <c r="A28" s="11" t="s">
         <v>22</v>
       </c>
@@ -1780,7 +1792,7 @@
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
   <dimension ref="A1:J84"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -1788,8 +1800,8 @@
     <col min="4" max="4" width="65" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="39.8909090909091" customWidth="1"/>
-    <col min="10" max="10" width="63.2181818181818" customWidth="1"/>
+    <col min="7" max="7" width="39.8888888888889" customWidth="1"/>
+    <col min="10" max="10" width="63.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:10">
@@ -1815,7 +1827,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" ht="42" spans="1:10">
+    <row r="2" ht="43.2" spans="1:10">
       <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
@@ -1831,192 +1843,194 @@
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="7" t="s">
+    </row>
+    <row r="3" ht="15" spans="1:10">
+      <c r="A3" s="2" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="3" ht="14.5" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="B3" s="6">
         <v>46310.5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" ht="30" spans="1:10">
+      <c r="A4" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" ht="29" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="B4" s="6">
         <v>46310.5416666667</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" ht="14.5" spans="1:10">
+    <row r="5" ht="15" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B5" s="6">
         <v>46310.75</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" ht="15" spans="1:10">
+      <c r="A6" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" ht="14.5" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="B6" s="6">
         <v>46311.4166666667</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" ht="115.2" spans="1:10">
+      <c r="A7" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" ht="112" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="B7" s="6">
         <v>46311.5277777778</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" ht="14.5" spans="1:10">
+    <row r="8" ht="15" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B8" s="6">
         <v>46311.625</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" ht="14.5" spans="1:10">
+    <row r="9" ht="15" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B9" s="6">
         <v>46312.5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" ht="14.5" spans="1:10">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B10" s="6">
         <v>46313.5833333333</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" ht="43.5" spans="1:10">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" ht="45" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B11" s="6">
         <v>46314.5833333333</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" ht="15" spans="1:10">
+      <c r="A12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="B12" s="6">
+        <v>46315.5416666667</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" ht="14.5" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" ht="14.5" spans="1:10">
+    <row r="13" ht="15" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2024,47 +2038,57 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" ht="14.5" spans="1:10">
-      <c r="A14" s="2"/>
+    <row r="14" ht="15" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" ht="14.5" spans="1:10">
-      <c r="A15" s="2"/>
+    <row r="15" ht="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" ht="14.5" spans="1:10">
-      <c r="A16" s="2"/>
+    <row r="16" ht="15" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" ht="14.5" spans="1:6">
-      <c r="A17" s="2"/>
+    <row r="17" ht="15" spans="1:6">
+      <c r="A17" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" ht="14.5" spans="1:6">
-      <c r="A18" s="2"/>
+    <row r="18" ht="15" spans="1:6">
+      <c r="A18" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" ht="14.5" spans="1:6">
+    <row r="19" ht="15" spans="1:6">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2072,7 +2096,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" ht="14.5" spans="1:6">
+    <row r="20" ht="15" spans="1:6">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2080,7 +2104,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" ht="14.5" spans="1:6">
+    <row r="21" ht="15" spans="1:6">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2088,7 +2112,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" ht="14.5" spans="1:6">
+    <row r="22" ht="15" spans="1:6">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2096,7 +2120,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" ht="14.5" spans="1:6">
+    <row r="23" ht="15" spans="1:6">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2104,7 +2128,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" ht="14.5" spans="1:6">
+    <row r="24" ht="15" spans="1:6">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2112,7 +2136,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" ht="14.5" spans="1:6">
+    <row r="25" ht="15" spans="1:6">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2120,7 +2144,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" ht="14.5" spans="1:6">
+    <row r="26" ht="15" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2128,7 +2152,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" ht="14.5" spans="1:6">
+    <row r="27" ht="15" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2136,7 +2160,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" ht="14.5" spans="1:6">
+    <row r="28" ht="15" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2144,7 +2168,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" ht="14.5" spans="1:6">
+    <row r="29" ht="15" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2152,7 +2176,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" ht="14.5" spans="1:6">
+    <row r="30" ht="15" spans="1:6">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2160,7 +2184,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" ht="14.5" spans="1:6">
+    <row r="31" ht="15" spans="1:6">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2168,7 +2192,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" ht="14.5" spans="1:6">
+    <row r="32" ht="15" spans="1:6">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2176,7 +2200,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" ht="14.5" spans="1:6">
+    <row r="33" ht="15" spans="1:6">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2184,7 +2208,7 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" ht="14.5" spans="1:6">
+    <row r="34" ht="15" spans="1:6">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2192,7 +2216,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" ht="14.5" spans="1:6">
+    <row r="35" ht="15" spans="1:6">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2200,7 +2224,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" ht="14.5" spans="1:6">
+    <row r="36" ht="15" spans="1:6">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2208,7 +2232,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" ht="14.5" spans="1:6">
+    <row r="37" ht="15" spans="1:6">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2216,7 +2240,7 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" ht="14.5" spans="1:6">
+    <row r="38" ht="15" spans="1:6">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2224,7 +2248,7 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
     </row>
-    <row r="39" ht="14.5" spans="1:6">
+    <row r="39" ht="15" spans="1:6">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2232,7 +2256,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" ht="14.5" spans="1:6">
+    <row r="40" ht="15" spans="1:6">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2240,7 +2264,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" ht="14.5" spans="1:6">
+    <row r="41" ht="15" spans="1:6">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2248,7 +2272,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" ht="14.5" spans="1:6">
+    <row r="42" ht="15" spans="1:6">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2256,7 +2280,7 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" ht="14.5" spans="1:6">
+    <row r="43" ht="15" spans="1:6">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2264,7 +2288,7 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" ht="14.5" spans="1:6">
+    <row r="44" ht="15" spans="1:6">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2272,7 +2296,7 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" ht="14.5" spans="1:6">
+    <row r="45" ht="15" spans="1:6">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2280,7 +2304,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" ht="14.5" spans="1:6">
+    <row r="46" ht="15" spans="1:6">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2288,7 +2312,7 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" ht="14.5" spans="1:6">
+    <row r="47" ht="15" spans="1:6">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -2296,7 +2320,7 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" ht="14.5" spans="1:6">
+    <row r="48" ht="15" spans="1:6">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2304,7 +2328,7 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" ht="14.5" spans="1:6">
+    <row r="49" ht="15" spans="1:6">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2312,7 +2336,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" ht="14.5" spans="1:6">
+    <row r="50" ht="15" spans="1:6">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2320,7 +2344,7 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
     </row>
-    <row r="51" ht="14.5" spans="1:6">
+    <row r="51" ht="15" spans="1:6">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2328,7 +2352,7 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" ht="14.5" spans="1:6">
+    <row r="52" ht="15" spans="1:6">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -2336,7 +2360,7 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" ht="14.5" spans="1:6">
+    <row r="53" ht="15" spans="1:6">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2344,7 +2368,7 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
     </row>
-    <row r="54" ht="14.5" spans="1:6">
+    <row r="54" ht="15" spans="1:6">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2352,7 +2376,7 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
     </row>
-    <row r="55" ht="14.5" spans="1:6">
+    <row r="55" ht="15" spans="1:6">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2360,7 +2384,7 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
     </row>
-    <row r="56" ht="14.5" spans="1:6">
+    <row r="56" ht="15" spans="1:6">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2368,7 +2392,7 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" ht="14.5" spans="1:6">
+    <row r="57" ht="15" spans="1:6">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2376,7 +2400,7 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" ht="14.5" spans="1:6">
+    <row r="58" ht="15" spans="1:6">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2384,7 +2408,7 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
     </row>
-    <row r="59" ht="14.5" spans="1:6">
+    <row r="59" ht="15" spans="1:6">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2392,7 +2416,7 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
     </row>
-    <row r="60" ht="14.5" spans="1:6">
+    <row r="60" ht="15" spans="1:6">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -2400,7 +2424,7 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
     </row>
-    <row r="61" ht="14.5" spans="1:6">
+    <row r="61" ht="15" spans="1:6">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2408,7 +2432,7 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
     </row>
-    <row r="62" ht="14.5" spans="1:6">
+    <row r="62" ht="15" spans="1:6">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -2416,7 +2440,7 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
     </row>
-    <row r="63" ht="14.5" spans="1:6">
+    <row r="63" ht="15" spans="1:6">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -2424,7 +2448,7 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
     </row>
-    <row r="64" ht="14.5" spans="1:6">
+    <row r="64" ht="15" spans="1:6">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -2432,7 +2456,7 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
     </row>
-    <row r="65" ht="14.5" spans="1:6">
+    <row r="65" ht="15" spans="1:6">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2440,7 +2464,7 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
     </row>
-    <row r="66" ht="14.5" spans="1:6">
+    <row r="66" ht="15" spans="1:6">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -2448,7 +2472,7 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
     </row>
-    <row r="67" ht="14.5" spans="1:6">
+    <row r="67" ht="15" spans="1:6">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2456,7 +2480,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
     </row>
-    <row r="68" ht="14.5" spans="1:6">
+    <row r="68" ht="15" spans="1:6">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -2464,7 +2488,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
     </row>
-    <row r="69" ht="14.5" spans="1:6">
+    <row r="69" ht="15" spans="1:6">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2472,7 +2496,7 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
     </row>
-    <row r="70" ht="14.5" spans="1:6">
+    <row r="70" ht="15" spans="1:6">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -2480,7 +2504,7 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
     </row>
-    <row r="71" ht="14.5" spans="1:6">
+    <row r="71" ht="15" spans="1:6">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -2488,7 +2512,7 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
     </row>
-    <row r="72" ht="14.5" spans="1:6">
+    <row r="72" ht="15" spans="1:6">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -2496,7 +2520,7 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
     </row>
-    <row r="73" ht="14.5" spans="1:6">
+    <row r="73" ht="15" spans="1:6">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -2504,7 +2528,7 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
     </row>
-    <row r="74" ht="14.5" spans="1:6">
+    <row r="74" ht="15" spans="1:6">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -2512,7 +2536,7 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
     </row>
-    <row r="75" ht="14.5" spans="1:6">
+    <row r="75" ht="15" spans="1:6">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2520,7 +2544,7 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
     </row>
-    <row r="76" ht="14.5" spans="1:6">
+    <row r="76" ht="15" spans="1:6">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -2528,7 +2552,7 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" ht="14.5" spans="1:6">
+    <row r="77" ht="15" spans="1:6">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -2536,7 +2560,7 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" ht="14.5" spans="1:6">
+    <row r="78" ht="15" spans="1:6">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -2544,7 +2568,7 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
     </row>
-    <row r="79" ht="14.5" spans="1:6">
+    <row r="79" ht="15" spans="1:6">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -2552,7 +2576,7 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
     </row>
-    <row r="80" ht="14.5" spans="1:6">
+    <row r="80" ht="15" spans="1:6">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2560,7 +2584,7 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
     </row>
-    <row r="81" ht="14.5" spans="1:6">
+    <row r="81" ht="15" spans="1:6">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -2568,7 +2592,7 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
     </row>
-    <row r="82" ht="14.5" spans="1:6">
+    <row r="82" ht="15" spans="1:6">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -2576,7 +2600,7 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
     </row>
-    <row r="83" ht="14.5" spans="1:6">
+    <row r="83" ht="15" spans="1:6">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -2584,7 +2608,7 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
     </row>
-    <row r="84" ht="14.5" spans="1:6">
+    <row r="84" ht="15" spans="1:6">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -2594,7 +2618,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C500">
+    <dataValidation type="list" allowBlank="1" sqref="C12 C2:C11 C13:C500">
       <formula1>"事发经过,医疗,沟通,园方行动,费用,其他"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2609,7 +2633,7 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="A1:F86"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2624,100 +2648,100 @@
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" ht="14.5" spans="1:6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B2" s="4">
         <v>46310</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D2" s="5">
         <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" ht="14.5" spans="1:6">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B3" s="4">
         <v>46310</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D3" s="5">
         <v>466</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" ht="14.5" spans="1:6">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B4" s="4">
         <v>46310</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" ht="14.5" spans="1:6">
+    <row r="5" ht="15" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B5" s="4">
         <v>46310</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D5" s="5">
         <v>80</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" ht="14.5" spans="1:6">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B6" s="4">
         <v>46310</v>
@@ -2727,9 +2751,9 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" ht="14.5" spans="1:6">
+    <row r="7" ht="15" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B7" s="4">
         <v>46311</v>
@@ -2739,125 +2763,125 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" ht="14.5" spans="1:6">
+    <row r="8" ht="15" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B8" s="4">
         <v>46311</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D8" s="5">
         <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" ht="14.5" spans="1:6">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B9" s="4">
         <v>46311</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D9" s="5">
         <v>16.45</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" ht="14.5" spans="1:6">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B10" s="4">
         <v>46312</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D10" s="5">
         <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" ht="14.5" spans="1:6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B11" s="4">
         <v>46312</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D11" s="5">
         <v>25.3</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" ht="14.5" spans="1:6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B12" s="4">
         <v>46312</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D12" s="5">
         <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" ht="14.5" spans="1:6">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B13" s="4">
         <v>46312</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D13" s="5">
         <v>225.76</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" ht="14.5" spans="1:6">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B14" s="4">
         <v>46313</v>
@@ -2867,9 +2891,9 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" ht="14.5" spans="1:6">
+    <row r="15" ht="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2877,9 +2901,9 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" ht="14.5" spans="1:6">
+    <row r="16" ht="15" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2887,9 +2911,9 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" ht="14.5" spans="1:6">
+    <row r="17" ht="15" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2897,9 +2921,9 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" ht="14.5" spans="1:6">
+    <row r="18" ht="15" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2907,9 +2931,9 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" ht="14.5" spans="1:6">
+    <row r="19" ht="15" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2917,9 +2941,9 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" ht="14.5" spans="1:6">
+    <row r="20" ht="15" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2927,9 +2951,9 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" ht="14.5" spans="1:6">
+    <row r="21" ht="15" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2937,9 +2961,9 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" ht="14.5" spans="1:6">
+    <row r="22" ht="15" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2947,9 +2971,9 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" ht="14.5" spans="1:6">
+    <row r="23" ht="15" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2957,7 +2981,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" ht="14.5" spans="1:6">
+    <row r="24" ht="15" spans="1:6">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2965,7 +2989,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" ht="14.5" spans="1:6">
+    <row r="25" ht="15" spans="1:6">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2973,7 +2997,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" ht="14.5" spans="1:6">
+    <row r="26" ht="15" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2981,7 +3005,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" ht="14.5" spans="1:6">
+    <row r="27" ht="15" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2989,7 +3013,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" ht="14.5" spans="1:6">
+    <row r="28" ht="15" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2997,7 +3021,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" ht="14.5" spans="1:6">
+    <row r="29" ht="15" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3005,7 +3029,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" ht="14.5" spans="1:6">
+    <row r="30" ht="15" spans="1:6">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3013,7 +3037,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" ht="14.5" spans="1:6">
+    <row r="31" ht="15" spans="1:6">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3021,7 +3045,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" ht="14.5" spans="1:6">
+    <row r="32" ht="15" spans="1:6">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3029,7 +3053,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" ht="14.5" spans="1:6">
+    <row r="33" ht="15" spans="1:6">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3037,7 +3061,7 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" ht="14.5" spans="1:6">
+    <row r="34" ht="15" spans="1:6">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3045,7 +3069,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" ht="14.5" spans="1:6">
+    <row r="35" ht="15" spans="1:6">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3055,7 +3079,7 @@
         <v>892.51</v>
       </c>
     </row>
-    <row r="36" ht="14.5" spans="1:6">
+    <row r="36" ht="15" spans="1:6">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3063,7 +3087,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" ht="14.5" spans="1:6">
+    <row r="37" ht="15" spans="1:6">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -3071,7 +3095,7 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" ht="14.5" spans="1:6">
+    <row r="38" ht="15" spans="1:6">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -3079,7 +3103,7 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
     </row>
-    <row r="39" ht="14.5" spans="1:6">
+    <row r="39" ht="15" spans="1:6">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -3087,7 +3111,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" ht="14.5" spans="1:6">
+    <row r="40" ht="15" spans="1:6">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3095,7 +3119,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" ht="14.5" spans="1:6">
+    <row r="41" ht="15" spans="1:6">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -3103,7 +3127,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" ht="14.5" spans="1:6">
+    <row r="42" ht="15" spans="1:6">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3111,7 +3135,7 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" ht="14.5" spans="1:6">
+    <row r="43" ht="15" spans="1:6">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3119,7 +3143,7 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" ht="14.5" spans="1:6">
+    <row r="44" ht="15" spans="1:6">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3127,7 +3151,7 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" ht="14.5" spans="1:6">
+    <row r="45" ht="15" spans="1:6">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -3135,7 +3159,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" ht="14.5" spans="1:6">
+    <row r="46" ht="15" spans="1:6">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3143,7 +3167,7 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" ht="14.5" spans="1:6">
+    <row r="47" ht="15" spans="1:6">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -3151,7 +3175,7 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" ht="14.5" spans="1:6">
+    <row r="48" ht="15" spans="1:6">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3159,7 +3183,7 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" ht="14.5" spans="1:6">
+    <row r="49" ht="15" spans="1:6">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -3167,7 +3191,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" ht="14.5" spans="1:6">
+    <row r="50" ht="15" spans="1:6">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3175,7 +3199,7 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
     </row>
-    <row r="51" ht="14.5" spans="1:6">
+    <row r="51" ht="15" spans="1:6">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -3183,7 +3207,7 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" ht="14.5" spans="1:6">
+    <row r="52" ht="15" spans="1:6">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3191,7 +3215,7 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" ht="14.5" spans="1:6">
+    <row r="53" ht="15" spans="1:6">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -3199,7 +3223,7 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
     </row>
-    <row r="54" ht="14.5" spans="1:6">
+    <row r="54" ht="15" spans="1:6">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3207,7 +3231,7 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
     </row>
-    <row r="55" ht="14.5" spans="1:6">
+    <row r="55" ht="15" spans="1:6">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3215,7 +3239,7 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
     </row>
-    <row r="56" ht="14.5" spans="1:6">
+    <row r="56" ht="15" spans="1:6">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3223,7 +3247,7 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" ht="14.5" spans="1:6">
+    <row r="57" ht="15" spans="1:6">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3231,7 +3255,7 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" ht="14.5" spans="1:6">
+    <row r="58" ht="15" spans="1:6">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3239,7 +3263,7 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
     </row>
-    <row r="59" ht="14.5" spans="1:6">
+    <row r="59" ht="15" spans="1:6">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3247,7 +3271,7 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
     </row>
-    <row r="60" ht="14.5" spans="1:6">
+    <row r="60" ht="15" spans="1:6">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -3255,7 +3279,7 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
     </row>
-    <row r="61" ht="14.5" spans="1:6">
+    <row r="61" ht="15" spans="1:6">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3263,7 +3287,7 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
     </row>
-    <row r="62" ht="14.5" spans="1:6">
+    <row r="62" ht="15" spans="1:6">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3271,7 +3295,7 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
     </row>
-    <row r="63" ht="14.5" spans="1:6">
+    <row r="63" ht="15" spans="1:6">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3279,7 +3303,7 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
     </row>
-    <row r="64" ht="14.5" spans="1:6">
+    <row r="64" ht="15" spans="1:6">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3287,7 +3311,7 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
     </row>
-    <row r="65" ht="14.5" spans="1:6">
+    <row r="65" ht="15" spans="1:6">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -3295,7 +3319,7 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
     </row>
-    <row r="66" ht="14.5" spans="1:6">
+    <row r="66" ht="15" spans="1:6">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -3303,7 +3327,7 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
     </row>
-    <row r="67" ht="14.5" spans="1:6">
+    <row r="67" ht="15" spans="1:6">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3311,7 +3335,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
     </row>
-    <row r="68" ht="14.5" spans="1:6">
+    <row r="68" ht="15" spans="1:6">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -3319,7 +3343,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
     </row>
-    <row r="69" ht="14.5" spans="1:6">
+    <row r="69" ht="15" spans="1:6">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3327,7 +3351,7 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
     </row>
-    <row r="70" ht="14.5" spans="1:6">
+    <row r="70" ht="15" spans="1:6">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3335,7 +3359,7 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
     </row>
-    <row r="71" ht="14.5" spans="1:6">
+    <row r="71" ht="15" spans="1:6">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3343,7 +3367,7 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
     </row>
-    <row r="72" ht="14.5" spans="1:6">
+    <row r="72" ht="15" spans="1:6">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3351,7 +3375,7 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
     </row>
-    <row r="73" ht="14.5" spans="1:6">
+    <row r="73" ht="15" spans="1:6">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3359,7 +3383,7 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
     </row>
-    <row r="74" ht="14.5" spans="1:6">
+    <row r="74" ht="15" spans="1:6">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3367,7 +3391,7 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
     </row>
-    <row r="75" ht="14.5" spans="1:6">
+    <row r="75" ht="15" spans="1:6">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3375,7 +3399,7 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
     </row>
-    <row r="76" ht="14.5" spans="1:6">
+    <row r="76" ht="15" spans="1:6">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3383,7 +3407,7 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" ht="14.5" spans="1:6">
+    <row r="77" ht="15" spans="1:6">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -3391,7 +3415,7 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" ht="14.5" spans="1:6">
+    <row r="78" ht="15" spans="1:6">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3399,7 +3423,7 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
     </row>
-    <row r="79" ht="14.5" spans="1:6">
+    <row r="79" ht="15" spans="1:6">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -3407,7 +3431,7 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
     </row>
-    <row r="80" ht="14.5" spans="1:6">
+    <row r="80" ht="15" spans="1:6">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3415,7 +3439,7 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
     </row>
-    <row r="81" ht="14.5" spans="1:6">
+    <row r="81" ht="15" spans="1:6">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3423,7 +3447,7 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
     </row>
-    <row r="82" ht="14.5" spans="1:6">
+    <row r="82" ht="15" spans="1:6">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -3431,7 +3455,7 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
     </row>
-    <row r="83" ht="14.5" spans="1:6">
+    <row r="83" ht="15" spans="1:6">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -3439,7 +3463,7 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
     </row>
-    <row r="84" ht="14.5" spans="1:6">
+    <row r="84" ht="15" spans="1:6">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -3447,7 +3471,7 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
     </row>
-    <row r="85" ht="14.5" spans="1:6">
+    <row r="85" ht="15" spans="1:6">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -3455,7 +3479,7 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
     </row>
-    <row r="86" ht="14.5" spans="1:6">
+    <row r="86" ht="15" spans="1:6">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -3480,7 +3504,7 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:G83"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -3493,96 +3517,96 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" ht="14.5" spans="1:7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:7">
       <c r="A2" s="4">
         <v>46310</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" ht="14.5" spans="1:7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:7">
       <c r="A3" s="4">
         <v>46311</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" ht="14.5" spans="1:7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:7">
       <c r="A4" s="4">
         <v>46312</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" ht="14.5" spans="1:7">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:7">
       <c r="A5" s="4">
         <v>46313</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -3590,12 +3614,12 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" ht="14.5" spans="1:7">
+    <row r="6" ht="15" spans="1:7">
       <c r="A6" s="4">
         <v>46314</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -3603,12 +3627,12 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" ht="14.5" spans="1:7">
+    <row r="7" ht="15" spans="1:7">
       <c r="A7" s="4">
         <v>46315</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -3616,12 +3640,12 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" ht="14.5" spans="1:7">
+    <row r="8" ht="15" spans="1:7">
       <c r="A8" s="4">
         <v>46316</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -3629,12 +3653,12 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" ht="14.5" spans="1:7">
+    <row r="9" ht="15" spans="1:7">
       <c r="A9" s="4">
         <v>46317</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -3642,7 +3666,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" ht="14.5" spans="1:7">
+    <row r="10" ht="15" spans="1:7">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -3651,7 +3675,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" ht="14.5" spans="1:7">
+    <row r="11" ht="15" spans="1:7">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -3660,7 +3684,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" ht="14.5" spans="1:7">
+    <row r="12" ht="15" spans="1:7">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -3669,7 +3693,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" ht="14.5" spans="1:7">
+    <row r="13" ht="15" spans="1:7">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -3678,7 +3702,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" ht="14.5" spans="1:7">
+    <row r="14" ht="15" spans="1:7">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -3687,7 +3711,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" ht="14.5" spans="1:7">
+    <row r="15" ht="15" spans="1:7">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -3696,7 +3720,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" ht="14.5" spans="1:7">
+    <row r="16" ht="15" spans="1:7">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -3705,7 +3729,7 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" ht="14.5" spans="1:7">
+    <row r="17" ht="15" spans="1:7">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -3714,7 +3738,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" ht="14.5" spans="1:7">
+    <row r="18" ht="15" spans="1:7">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -3723,7 +3747,7 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" ht="14.5" spans="1:7">
+    <row r="19" ht="15" spans="1:7">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -3732,7 +3756,7 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" ht="14.5" spans="1:7">
+    <row r="20" ht="15" spans="1:7">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3741,7 +3765,7 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" ht="14.5" spans="1:7">
+    <row r="21" ht="15" spans="1:7">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -3750,7 +3774,7 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" ht="14.5" spans="1:7">
+    <row r="22" ht="15" spans="1:7">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -3759,7 +3783,7 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" ht="14.5" spans="1:7">
+    <row r="23" ht="15" spans="1:7">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -3768,7 +3792,7 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" ht="14.5" spans="1:7">
+    <row r="24" ht="15" spans="1:7">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3777,7 +3801,7 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" ht="14.5" spans="1:7">
+    <row r="25" ht="15" spans="1:7">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3786,7 +3810,7 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" ht="14.5" spans="1:7">
+    <row r="26" ht="15" spans="1:7">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3795,7 +3819,7 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" ht="14.5" spans="1:7">
+    <row r="27" ht="15" spans="1:7">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3804,7 +3828,7 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" ht="14.5" spans="1:7">
+    <row r="28" ht="15" spans="1:7">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3813,7 +3837,7 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" ht="14.5" spans="1:7">
+    <row r="29" ht="15" spans="1:7">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3822,7 +3846,7 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" ht="14.5" spans="1:7">
+    <row r="30" ht="15" spans="1:7">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3831,7 +3855,7 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" ht="14.5" spans="1:7">
+    <row r="31" ht="15" spans="1:7">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3840,7 +3864,7 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" ht="14.5" spans="1:7">
+    <row r="32" ht="15" spans="1:7">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3849,7 +3873,7 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" ht="14.5" spans="1:7">
+    <row r="33" ht="15" spans="1:7">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3858,7 +3882,7 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" ht="14.5" spans="1:7">
+    <row r="34" ht="15" spans="1:7">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3867,7 +3891,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" ht="14.5" spans="1:7">
+    <row r="35" ht="15" spans="1:7">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3876,7 +3900,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" ht="14.5" spans="1:7">
+    <row r="36" ht="15" spans="1:7">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3885,7 +3909,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" ht="14.5" spans="1:7">
+    <row r="37" ht="15" spans="1:7">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -3894,7 +3918,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" ht="14.5" spans="1:7">
+    <row r="38" ht="15" spans="1:7">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -3903,7 +3927,7 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" ht="14.5" spans="1:7">
+    <row r="39" ht="15" spans="1:7">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -3912,7 +3936,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" ht="14.5" spans="1:7">
+    <row r="40" ht="15" spans="1:7">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3921,7 +3945,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" ht="14.5" spans="1:7">
+    <row r="41" ht="15" spans="1:7">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -3930,7 +3954,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" ht="14.5" spans="1:7">
+    <row r="42" ht="15" spans="1:7">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3939,7 +3963,7 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" ht="14.5" spans="1:7">
+    <row r="43" ht="15" spans="1:7">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3948,7 +3972,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" ht="14.5" spans="1:7">
+    <row r="44" ht="15" spans="1:7">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3957,7 +3981,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" ht="14.5" spans="1:7">
+    <row r="45" ht="15" spans="1:7">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -3966,7 +3990,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" ht="14.5" spans="1:7">
+    <row r="46" ht="15" spans="1:7">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3975,7 +3999,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" ht="14.5" spans="1:7">
+    <row r="47" ht="15" spans="1:7">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -3984,7 +4008,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" ht="14.5" spans="1:7">
+    <row r="48" ht="15" spans="1:7">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3993,7 +4017,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" ht="14.5" spans="1:7">
+    <row r="49" ht="15" spans="1:7">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4002,7 +4026,7 @@
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
     </row>
-    <row r="50" ht="14.5" spans="1:7">
+    <row r="50" ht="15" spans="1:7">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -4011,7 +4035,7 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
     </row>
-    <row r="51" ht="14.5" spans="1:7">
+    <row r="51" ht="15" spans="1:7">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -4020,7 +4044,7 @@
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
     </row>
-    <row r="52" ht="14.5" spans="1:7">
+    <row r="52" ht="15" spans="1:7">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -4029,7 +4053,7 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
     </row>
-    <row r="53" ht="14.5" spans="1:7">
+    <row r="53" ht="15" spans="1:7">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -4038,7 +4062,7 @@
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
     </row>
-    <row r="54" ht="14.5" spans="1:7">
+    <row r="54" ht="15" spans="1:7">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -4047,7 +4071,7 @@
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
     </row>
-    <row r="55" ht="14.5" spans="1:7">
+    <row r="55" ht="15" spans="1:7">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -4056,7 +4080,7 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
     </row>
-    <row r="56" ht="14.5" spans="1:7">
+    <row r="56" ht="15" spans="1:7">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -4065,7 +4089,7 @@
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
     </row>
-    <row r="57" ht="14.5" spans="1:7">
+    <row r="57" ht="15" spans="1:7">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -4074,7 +4098,7 @@
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
     </row>
-    <row r="58" ht="14.5" spans="1:7">
+    <row r="58" ht="15" spans="1:7">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -4083,7 +4107,7 @@
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
     </row>
-    <row r="59" ht="14.5" spans="1:7">
+    <row r="59" ht="15" spans="1:7">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -4092,7 +4116,7 @@
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
     </row>
-    <row r="60" ht="14.5" spans="1:7">
+    <row r="60" ht="15" spans="1:7">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -4101,7 +4125,7 @@
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
     </row>
-    <row r="61" ht="14.5" spans="1:7">
+    <row r="61" ht="15" spans="1:7">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -4110,7 +4134,7 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
     </row>
-    <row r="62" ht="14.5" spans="1:7">
+    <row r="62" ht="15" spans="1:7">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -4119,7 +4143,7 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
     </row>
-    <row r="63" ht="14.5" spans="1:7">
+    <row r="63" ht="15" spans="1:7">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -4128,7 +4152,7 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
     </row>
-    <row r="64" ht="14.5" spans="1:7">
+    <row r="64" ht="15" spans="1:7">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -4137,7 +4161,7 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
     </row>
-    <row r="65" ht="14.5" spans="1:7">
+    <row r="65" ht="15" spans="1:7">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -4146,7 +4170,7 @@
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
     </row>
-    <row r="66" ht="14.5" spans="1:7">
+    <row r="66" ht="15" spans="1:7">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -4155,7 +4179,7 @@
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
     </row>
-    <row r="67" ht="14.5" spans="1:7">
+    <row r="67" ht="15" spans="1:7">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -4164,7 +4188,7 @@
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
     </row>
-    <row r="68" ht="14.5" spans="1:7">
+    <row r="68" ht="15" spans="1:7">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -4173,7 +4197,7 @@
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
     </row>
-    <row r="69" ht="14.5" spans="1:7">
+    <row r="69" ht="15" spans="1:7">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -4182,7 +4206,7 @@
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
     </row>
-    <row r="70" ht="14.5" spans="1:7">
+    <row r="70" ht="15" spans="1:7">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -4191,7 +4215,7 @@
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
     </row>
-    <row r="71" ht="14.5" spans="1:7">
+    <row r="71" ht="15" spans="1:7">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -4200,7 +4224,7 @@
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
     </row>
-    <row r="72" ht="14.5" spans="1:7">
+    <row r="72" ht="15" spans="1:7">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -4209,7 +4233,7 @@
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
     </row>
-    <row r="73" ht="14.5" spans="1:7">
+    <row r="73" ht="15" spans="1:7">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -4218,7 +4242,7 @@
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
     </row>
-    <row r="74" ht="14.5" spans="1:7">
+    <row r="74" ht="15" spans="1:7">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -4227,7 +4251,7 @@
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
     </row>
-    <row r="75" ht="14.5" spans="1:7">
+    <row r="75" ht="15" spans="1:7">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -4236,7 +4260,7 @@
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
     </row>
-    <row r="76" ht="14.5" spans="1:7">
+    <row r="76" ht="15" spans="1:7">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -4245,7 +4269,7 @@
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
     </row>
-    <row r="77" ht="14.5" spans="1:7">
+    <row r="77" ht="15" spans="1:7">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4254,7 +4278,7 @@
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
     </row>
-    <row r="78" ht="14.5" spans="1:7">
+    <row r="78" ht="15" spans="1:7">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -4263,7 +4287,7 @@
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
     </row>
-    <row r="79" ht="14.5" spans="1:7">
+    <row r="79" ht="15" spans="1:7">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -4272,7 +4296,7 @@
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
     </row>
-    <row r="80" ht="14.5" spans="1:7">
+    <row r="80" ht="15" spans="1:7">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -4281,7 +4305,7 @@
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
     </row>
-    <row r="81" ht="14.5" spans="1:7">
+    <row r="81" ht="15" spans="1:7">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -4290,7 +4314,7 @@
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
     </row>
-    <row r="82" ht="14.5" spans="1:7">
+    <row r="82" ht="15" spans="1:7">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -4299,7 +4323,7 @@
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
     </row>
-    <row r="83" ht="14.5" spans="1:7">
+    <row r="83" ht="15" spans="1:7">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -4325,7 +4349,7 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:F82"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4340,82 +4364,82 @@
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" ht="14.5" spans="1:6">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" ht="14.5" spans="1:6">
+    <row r="3" ht="15" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" ht="14.5" spans="1:6">
+    <row r="4" ht="15" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" ht="14.5" spans="1:6">
+    <row r="5" ht="15" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" ht="14.5" spans="1:6">
+    <row r="6" ht="15" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -4423,9 +4447,9 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" ht="14.5" spans="1:6">
+    <row r="7" ht="15" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -4433,9 +4457,9 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" ht="14.5" spans="1:6">
+    <row r="8" ht="15" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -4443,7 +4467,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" ht="14.5" spans="1:6">
+    <row r="9" ht="15" spans="1:6">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -4451,7 +4475,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" ht="14.5" spans="1:6">
+    <row r="10" ht="15" spans="1:6">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -4459,7 +4483,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" ht="14.5" spans="1:6">
+    <row r="11" ht="15" spans="1:6">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -4467,7 +4491,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" ht="14.5" spans="1:6">
+    <row r="12" ht="15" spans="1:6">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -4475,7 +4499,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" ht="14.5" spans="1:6">
+    <row r="13" ht="15" spans="1:6">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -4483,7 +4507,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" ht="14.5" spans="1:6">
+    <row r="14" ht="15" spans="1:6">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -4491,7 +4515,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" ht="14.5" spans="1:6">
+    <row r="15" ht="15" spans="1:6">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -4499,7 +4523,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" ht="14.5" spans="1:6">
+    <row r="16" ht="15" spans="1:6">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -4507,7 +4531,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" ht="14.5" spans="1:6">
+    <row r="17" ht="15" spans="1:6">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -4515,7 +4539,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" ht="14.5" spans="1:6">
+    <row r="18" ht="15" spans="1:6">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -4523,7 +4547,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" ht="14.5" spans="1:6">
+    <row r="19" ht="15" spans="1:6">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -4531,7 +4555,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" ht="14.5" spans="1:6">
+    <row r="20" ht="15" spans="1:6">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -4539,7 +4563,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" ht="14.5" spans="1:6">
+    <row r="21" ht="15" spans="1:6">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -4547,7 +4571,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" ht="14.5" spans="1:6">
+    <row r="22" ht="15" spans="1:6">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4555,7 +4579,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" ht="14.5" spans="1:6">
+    <row r="23" ht="15" spans="1:6">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4563,7 +4587,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" ht="14.5" spans="1:6">
+    <row r="24" ht="15" spans="1:6">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4571,7 +4595,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" ht="14.5" spans="1:6">
+    <row r="25" ht="15" spans="1:6">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -4579,7 +4603,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" ht="14.5" spans="1:6">
+    <row r="26" ht="15" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -4587,7 +4611,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" ht="14.5" spans="1:6">
+    <row r="27" ht="15" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -4595,7 +4619,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" ht="14.5" spans="1:6">
+    <row r="28" ht="15" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -4603,7 +4627,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" ht="14.5" spans="1:6">
+    <row r="29" ht="15" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -4611,7 +4635,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" ht="14.5" spans="1:6">
+    <row r="30" ht="15" spans="1:6">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -4619,7 +4643,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" ht="14.5" spans="1:6">
+    <row r="31" ht="15" spans="1:6">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -4627,7 +4651,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" ht="14.5" spans="1:6">
+    <row r="32" ht="15" spans="1:6">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -4635,7 +4659,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" ht="14.5" spans="1:6">
+    <row r="33" ht="15" spans="1:6">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -4643,7 +4667,7 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" ht="14.5" spans="1:6">
+    <row r="34" ht="15" spans="1:6">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -4651,7 +4675,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" ht="14.5" spans="1:6">
+    <row r="35" ht="15" spans="1:6">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -4659,7 +4683,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" ht="14.5" spans="1:6">
+    <row r="36" ht="15" spans="1:6">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -4667,7 +4691,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" ht="14.5" spans="1:6">
+    <row r="37" ht="15" spans="1:6">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4675,7 +4699,7 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" ht="14.5" spans="1:6">
+    <row r="38" ht="15" spans="1:6">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4683,7 +4707,7 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
     </row>
-    <row r="39" ht="14.5" spans="1:6">
+    <row r="39" ht="15" spans="1:6">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4691,7 +4715,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" ht="14.5" spans="1:6">
+    <row r="40" ht="15" spans="1:6">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4699,7 +4723,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" ht="14.5" spans="1:6">
+    <row r="41" ht="15" spans="1:6">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4707,7 +4731,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" ht="14.5" spans="1:6">
+    <row r="42" ht="15" spans="1:6">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4715,7 +4739,7 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" ht="14.5" spans="1:6">
+    <row r="43" ht="15" spans="1:6">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4723,7 +4747,7 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" ht="14.5" spans="1:6">
+    <row r="44" ht="15" spans="1:6">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4731,7 +4755,7 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" ht="14.5" spans="1:6">
+    <row r="45" ht="15" spans="1:6">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4739,7 +4763,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" ht="14.5" spans="1:6">
+    <row r="46" ht="15" spans="1:6">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4747,7 +4771,7 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" ht="14.5" spans="1:6">
+    <row r="47" ht="15" spans="1:6">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4755,7 +4779,7 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" ht="14.5" spans="1:6">
+    <row r="48" ht="15" spans="1:6">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4763,7 +4787,7 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" ht="14.5" spans="1:6">
+    <row r="49" ht="15" spans="1:6">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4771,7 +4795,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" ht="14.5" spans="1:6">
+    <row r="50" ht="15" spans="1:6">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -4779,7 +4803,7 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
     </row>
-    <row r="51" ht="14.5" spans="1:6">
+    <row r="51" ht="15" spans="1:6">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -4787,7 +4811,7 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" ht="14.5" spans="1:6">
+    <row r="52" ht="15" spans="1:6">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -4795,7 +4819,7 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" ht="14.5" spans="1:6">
+    <row r="53" ht="15" spans="1:6">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -4803,7 +4827,7 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
     </row>
-    <row r="54" ht="14.5" spans="1:6">
+    <row r="54" ht="15" spans="1:6">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -4811,7 +4835,7 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
     </row>
-    <row r="55" ht="14.5" spans="1:6">
+    <row r="55" ht="15" spans="1:6">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -4819,7 +4843,7 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
     </row>
-    <row r="56" ht="14.5" spans="1:6">
+    <row r="56" ht="15" spans="1:6">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -4827,7 +4851,7 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" ht="14.5" spans="1:6">
+    <row r="57" ht="15" spans="1:6">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -4835,7 +4859,7 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" ht="14.5" spans="1:6">
+    <row r="58" ht="15" spans="1:6">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -4843,7 +4867,7 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
     </row>
-    <row r="59" ht="14.5" spans="1:6">
+    <row r="59" ht="15" spans="1:6">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -4851,7 +4875,7 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
     </row>
-    <row r="60" ht="14.5" spans="1:6">
+    <row r="60" ht="15" spans="1:6">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -4859,7 +4883,7 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
     </row>
-    <row r="61" ht="14.5" spans="1:6">
+    <row r="61" ht="15" spans="1:6">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -4867,7 +4891,7 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
     </row>
-    <row r="62" ht="14.5" spans="1:6">
+    <row r="62" ht="15" spans="1:6">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -4875,7 +4899,7 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
     </row>
-    <row r="63" ht="14.5" spans="1:6">
+    <row r="63" ht="15" spans="1:6">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -4883,7 +4907,7 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
     </row>
-    <row r="64" ht="14.5" spans="1:6">
+    <row r="64" ht="15" spans="1:6">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -4891,7 +4915,7 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
     </row>
-    <row r="65" ht="14.5" spans="1:6">
+    <row r="65" ht="15" spans="1:6">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -4899,7 +4923,7 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
     </row>
-    <row r="66" ht="14.5" spans="1:6">
+    <row r="66" ht="15" spans="1:6">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -4907,7 +4931,7 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
     </row>
-    <row r="67" ht="14.5" spans="1:6">
+    <row r="67" ht="15" spans="1:6">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -4915,7 +4939,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
     </row>
-    <row r="68" ht="14.5" spans="1:6">
+    <row r="68" ht="15" spans="1:6">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -4923,7 +4947,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
     </row>
-    <row r="69" ht="14.5" spans="1:6">
+    <row r="69" ht="15" spans="1:6">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -4931,7 +4955,7 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
     </row>
-    <row r="70" ht="14.5" spans="1:6">
+    <row r="70" ht="15" spans="1:6">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -4939,7 +4963,7 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
     </row>
-    <row r="71" ht="14.5" spans="1:6">
+    <row r="71" ht="15" spans="1:6">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -4947,7 +4971,7 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
     </row>
-    <row r="72" ht="14.5" spans="1:6">
+    <row r="72" ht="15" spans="1:6">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -4955,7 +4979,7 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
     </row>
-    <row r="73" ht="14.5" spans="1:6">
+    <row r="73" ht="15" spans="1:6">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -4963,7 +4987,7 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
     </row>
-    <row r="74" ht="14.5" spans="1:6">
+    <row r="74" ht="15" spans="1:6">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -4971,7 +4995,7 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
     </row>
-    <row r="75" ht="14.5" spans="1:6">
+    <row r="75" ht="15" spans="1:6">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -4979,7 +5003,7 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
     </row>
-    <row r="76" ht="14.5" spans="1:6">
+    <row r="76" ht="15" spans="1:6">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -4987,7 +5011,7 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" ht="14.5" spans="1:6">
+    <row r="77" ht="15" spans="1:6">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4995,7 +5019,7 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" ht="14.5" spans="1:6">
+    <row r="78" ht="15" spans="1:6">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -5003,7 +5027,7 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
     </row>
-    <row r="79" ht="14.5" spans="1:6">
+    <row r="79" ht="15" spans="1:6">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -5011,7 +5035,7 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
     </row>
-    <row r="80" ht="14.5" spans="1:6">
+    <row r="80" ht="15" spans="1:6">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -5019,7 +5043,7 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
     </row>
-    <row r="81" ht="14.5" spans="1:6">
+    <row r="81" ht="15" spans="1:6">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -5027,7 +5051,7 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
     </row>
-    <row r="82" ht="14.5" spans="1:6">
+    <row r="82" ht="15" spans="1:6">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>

--- a/幼儿受伤处理记录/幼儿受伤记录表.xlsx
+++ b/幼儿受伤处理记录/幼儿受伤记录表.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="170">
   <si>
     <t>幼儿受伤记录表 · 使用说明（详细版见同目录《使用说明.txt》）</t>
   </si>
@@ -289,6 +289,9 @@
     <t>A012</t>
   </si>
   <si>
+    <t>杭整复查，拆线</t>
+  </si>
+  <si>
     <t>A013</t>
   </si>
   <si>
@@ -424,21 +427,36 @@
     <t>B014</t>
   </si>
   <si>
+    <t>手术费</t>
+  </si>
+  <si>
     <t>B015</t>
   </si>
   <si>
+    <t>挂号</t>
+  </si>
+  <si>
     <t>B016</t>
   </si>
   <si>
+    <t>换药</t>
+  </si>
+  <si>
     <t>B017</t>
   </si>
   <si>
+    <t>打车</t>
+  </si>
+  <si>
     <t>B018</t>
   </si>
   <si>
     <t>B019</t>
   </si>
   <si>
+    <t>配药</t>
+  </si>
+  <si>
     <t>B020</t>
   </si>
   <si>
@@ -505,6 +523,9 @@
     <t>第4天</t>
   </si>
   <si>
+    <t>手术</t>
+  </si>
+  <si>
     <t>第5天</t>
   </si>
   <si>
@@ -515,6 +536,9 @@
   </si>
   <si>
     <t>第8天</t>
+  </si>
+  <si>
+    <t>拆线</t>
   </si>
   <si>
     <t>姓名</t>
@@ -1248,7 +1272,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1263,6 +1287,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1641,142 +1668,142 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.4" spans="1:1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="16.2" spans="1:1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:1">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:1">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:1">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="16.2" spans="1:1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:1">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:1">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" ht="16.2" spans="1:1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:1">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:1">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:1">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" ht="15" spans="1:1">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" ht="16.2" spans="1:1">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" ht="15.6" spans="1:1">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:1">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" ht="16.2" spans="1:1">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" ht="15" spans="1:1">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" ht="15" spans="1:1">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" ht="15" spans="1:1">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="15" spans="1:1">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="12" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1831,7 +1858,7 @@
       <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>46310.46875</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1844,7 +1871,7 @@
         <v>33</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1852,7 +1879,7 @@
       <c r="A3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>46310.5</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1868,7 +1895,7 @@
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>46310.5416666667</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1884,7 +1911,7 @@
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>46310.75</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1902,7 +1929,7 @@
       <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>46311.4166666667</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1920,7 +1947,7 @@
       <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>46311.5277777778</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1931,16 +1958,16 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="7"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" ht="15" spans="1:10">
       <c r="A8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>46311.625</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1956,7 +1983,7 @@
       <c r="A9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>46312.5</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1977,7 +2004,7 @@
       <c r="A10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>46313.5833333333</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1990,7 +2017,7 @@
         <v>55</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1998,7 +2025,7 @@
       <c r="A11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>46314.5833333333</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -2016,7 +2043,7 @@
       <c r="A12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>46315.5416666667</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -2032,15 +2059,21 @@
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="B13" s="7">
+        <v>46317.4166666667</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
     <row r="14" ht="15" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2050,7 +2083,7 @@
     </row>
     <row r="15" ht="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2060,7 +2093,7 @@
     </row>
     <row r="16" ht="15" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2070,7 +2103,7 @@
     </row>
     <row r="17" ht="15" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2080,7 +2113,7 @@
     </row>
     <row r="18" ht="15" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2618,7 +2651,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C12 C2:C11 C13:C500">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C500">
       <formula1>"事发经过,医疗,沟通,园方行动,费用,其他"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2648,100 +2681,100 @@
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="4">
         <v>46310</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D2" s="5">
         <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="4">
         <v>46310</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" s="5">
         <v>466</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" s="4">
         <v>46310</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" ht="15" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" s="4">
         <v>46310</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" s="5">
         <v>80</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B6" s="4">
         <v>46310</v>
@@ -2753,7 +2786,7 @@
     </row>
     <row r="7" ht="15" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" s="4">
         <v>46311</v>
@@ -2765,39 +2798,39 @@
     </row>
     <row r="8" ht="15" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B8" s="4">
         <v>46311</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="5">
         <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" s="4">
         <v>46311</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" s="5">
         <v>16.45</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>52</v>
@@ -2805,155 +2838,187 @@
     </row>
     <row r="10" ht="15" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" s="4">
         <v>46312</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" s="5">
         <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B11" s="4">
         <v>46312</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D11" s="5">
         <v>25.3</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B12" s="4">
         <v>46312</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" s="5">
         <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B13" s="4">
         <v>46312</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D13" s="5">
         <v>225.76</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B14" s="4">
         <v>46313</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="5">
+        <v>7434.85</v>
+      </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
     <row r="15" ht="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="5"/>
+        <v>113</v>
+      </c>
+      <c r="B15" s="6">
+        <v>46315</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="5">
+        <v>15.3</v>
+      </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
     <row r="16" ht="15" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="5">
+        <v>14</v>
+      </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
     <row r="17" ht="15" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="5">
+        <v>40.5</v>
+      </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" ht="15" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="5"/>
+        <v>119</v>
+      </c>
+      <c r="B18" s="6">
+        <v>46317</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="5">
+        <v>25.3</v>
+      </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
     <row r="19" ht="15" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1581</v>
+      </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
     <row r="20" ht="15" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="5">
+        <v>49.65</v>
+      </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
     <row r="21" ht="15" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2963,7 +3028,7 @@
     </row>
     <row r="22" ht="15" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2973,7 +3038,7 @@
     </row>
     <row r="23" ht="15" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -3076,7 +3141,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="5">
         <f>SUM(D:D)</f>
-        <v>892.51</v>
+        <v>10053.11</v>
       </c>
     </row>
     <row r="36" ht="15" spans="1:6">
@@ -3517,25 +3582,25 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:7">
@@ -3543,20 +3608,20 @@
         <v>46310</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:7">
@@ -3564,20 +3629,20 @@
         <v>46311</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:7">
@@ -3585,20 +3650,20 @@
         <v>46312</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:7">
@@ -3606,11 +3671,12 @@
         <v>46313</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>143</v>
+      </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
@@ -3619,7 +3685,7 @@
         <v>46314</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -3632,11 +3698,13 @@
         <v>46315</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
@@ -3645,7 +3713,7 @@
         <v>46316</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -3658,16 +3726,19 @@
         <v>46317</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>148</v>
+      </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" ht="15" spans="1:7">
-      <c r="A10" s="2"/>
+      <c r="A10" s="4">
+        <v>46318</v>
+      </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -3676,7 +3747,9 @@
       <c r="G10" s="2"/>
     </row>
     <row r="11" ht="15" spans="1:7">
-      <c r="A11" s="2"/>
+      <c r="A11" s="4">
+        <v>46319</v>
+      </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -3685,7 +3758,9 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" ht="15" spans="1:7">
-      <c r="A12" s="2"/>
+      <c r="A12" s="4">
+        <v>46320</v>
+      </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -3694,7 +3769,9 @@
       <c r="G12" s="2"/>
     </row>
     <row r="13" ht="15" spans="1:7">
-      <c r="A13" s="2"/>
+      <c r="A13" s="4">
+        <v>46321</v>
+      </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -3703,7 +3780,9 @@
       <c r="G13" s="2"/>
     </row>
     <row r="14" ht="15" spans="1:7">
-      <c r="A14" s="2"/>
+      <c r="A14" s="4">
+        <v>46322</v>
+      </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -3712,7 +3791,9 @@
       <c r="G14" s="2"/>
     </row>
     <row r="15" ht="15" spans="1:7">
-      <c r="A15" s="2"/>
+      <c r="A15" s="4">
+        <v>46323</v>
+      </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -3721,7 +3802,9 @@
       <c r="G15" s="2"/>
     </row>
     <row r="16" ht="15" spans="1:7">
-      <c r="A16" s="2"/>
+      <c r="A16" s="4">
+        <v>46324</v>
+      </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -3730,7 +3813,9 @@
       <c r="G16" s="2"/>
     </row>
     <row r="17" ht="15" spans="1:7">
-      <c r="A17" s="2"/>
+      <c r="A17" s="4">
+        <v>46325</v>
+      </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -3739,7 +3824,9 @@
       <c r="G17" s="2"/>
     </row>
     <row r="18" ht="15" spans="1:7">
-      <c r="A18" s="2"/>
+      <c r="A18" s="4">
+        <v>46326</v>
+      </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -3748,7 +3835,9 @@
       <c r="G18" s="2"/>
     </row>
     <row r="19" ht="15" spans="1:7">
-      <c r="A19" s="2"/>
+      <c r="A19" s="4">
+        <v>46327</v>
+      </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -4334,7 +4423,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C500">
+    <dataValidation type="list" allowBlank="1" sqref="E5 E9 C2:C4 C6:C8 C10:C500">
       <formula1>"正常结痂,轻微红肿,红肿加重,渗液,出血,化脓(立即就医),肿胀消退,开始脱痂,疤痕期"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4364,74 +4453,74 @@
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F2" s="4"/>
     </row>
     <row r="3" ht="15" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" ht="15" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" ht="15" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -4439,7 +4528,7 @@
     </row>
     <row r="6" ht="15" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -4449,7 +4538,7 @@
     </row>
     <row r="7" ht="15" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -4459,7 +4548,7 @@
     </row>
     <row r="8" ht="15" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
